--- a/mystkdata/output.xlsx
+++ b/mystkdata/output.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="68">
   <si>
     <t>Qty</t>
   </si>
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2533,242 +2533,242 @@
     <row r="159" spans="1:4">
       <c r="A159" s="1"/>
       <c r="B159" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C159">
-        <v>0</v>
-      </c>
-      <c r="D159">
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
         <v>15748.2756</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
-      <c r="A160" s="1" t="s">
+    <row r="161" spans="1:4">
+      <c r="A161" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B161" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C160">
+      <c r="C161">
         <v>1.638</v>
       </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="1"/>
-      <c r="B161" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
       <c r="D161">
-        <v>26583.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="1"/>
       <c r="B162" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C162">
         <v>0</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>26583.5</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="1"/>
       <c r="B163" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C163">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="D163">
-        <v>1215.916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="1"/>
       <c r="B164" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D164">
-        <v>11562</v>
+        <v>1215.916</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="1"/>
       <c r="B165" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C165">
         <v>0</v>
       </c>
       <c r="D165">
-        <v>7200</v>
+        <v>11562</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="1"/>
       <c r="B166" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C166">
-        <v>0</v>
-      </c>
-      <c r="D166">
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
         <v>1250</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
-      <c r="A167" s="1" t="s">
+    <row r="168" spans="1:4">
+      <c r="A168" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-      <c r="D167">
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
         <v>1750</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168" s="1"/>
-      <c r="B168" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C168">
-        <v>1.418</v>
-      </c>
-      <c r="D168">
-        <v>27158.6</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="1"/>
       <c r="B169" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1.418</v>
       </c>
       <c r="D169">
-        <v>24533.55</v>
+        <v>27158.6</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="1"/>
       <c r="B170" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C170">
         <v>0</v>
       </c>
       <c r="D170">
-        <v>16640</v>
+        <v>24533.55</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="1"/>
       <c r="B171" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C171">
         <v>0</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>16640</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="1"/>
       <c r="B172" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C172">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D172">
-        <v>1311.752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="1"/>
       <c r="B173" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D173">
-        <v>11280</v>
+        <v>1311.752</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="1"/>
       <c r="B174" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>11280</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="1"/>
       <c r="B175" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C175">
         <v>0</v>
       </c>
       <c r="D175">
-        <v>7680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="1"/>
       <c r="B176" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C176">
         <v>0</v>
       </c>
       <c r="D176">
-        <v>1250</v>
+        <v>7680</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="1"/>
       <c r="B177" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C177">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="1"/>
       <c r="B178" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C178">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -2777,292 +2777,292 @@
     <row r="179" spans="1:4">
       <c r="A179" s="1"/>
       <c r="B179" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D179">
-        <v>9000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="1"/>
       <c r="B180" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+      <c r="D180">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C180">
+      <c r="C181">
         <v>1</v>
       </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
-      <c r="A181" s="1" t="s">
+      <c r="D181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B182" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C181">
-        <v>0</v>
-      </c>
-      <c r="D181">
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182">
         <v>19553.18</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
-      <c r="A182" s="1"/>
-      <c r="B182" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
-      </c>
-      <c r="D182">
-        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="1"/>
       <c r="B183" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C183">
         <v>0</v>
       </c>
       <c r="D183">
-        <v>1311.752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="1"/>
       <c r="B184" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C184">
         <v>0</v>
       </c>
       <c r="D184">
-        <v>11280</v>
+        <v>1311.752</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="1"/>
       <c r="B185" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C185">
         <v>0</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>11280</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="1"/>
       <c r="B186" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C186">
         <v>0</v>
       </c>
       <c r="D186">
-        <v>7680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="1"/>
       <c r="B187" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C187">
         <v>0</v>
       </c>
       <c r="D187">
-        <v>1075</v>
+        <v>7680</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="1"/>
       <c r="B188" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
-      <c r="D188">
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
         <v>5700</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
-      <c r="A189" s="1" t="s">
+    <row r="190" spans="1:4">
+      <c r="A190" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B190" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C189">
-        <v>0</v>
-      </c>
-      <c r="D189">
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
         <v>24988.49</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="1"/>
       <c r="B191" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C191">
         <v>0</v>
       </c>
       <c r="D191">
-        <v>1311.752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="1"/>
       <c r="B192" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C192">
         <v>0</v>
       </c>
       <c r="D192">
-        <v>10857</v>
+        <v>1311.752</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="1"/>
       <c r="B193" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C193">
         <v>0</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>10857</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="1"/>
       <c r="B194" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C194">
         <v>0</v>
       </c>
       <c r="D194">
-        <v>7680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="1"/>
       <c r="B195" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>7680</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C195">
-        <v>0</v>
-      </c>
-      <c r="D195">
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
         <v>1200</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
-      <c r="A196" s="1" t="s">
+    <row r="197" spans="1:4">
+      <c r="A197" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B197" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C196">
+      <c r="C197">
         <v>3.133</v>
       </c>
-      <c r="D196">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
-      <c r="A197" s="1"/>
-      <c r="B197" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C197">
-        <v>0</v>
-      </c>
       <c r="D197">
-        <v>1550</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="1"/>
       <c r="B198" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C198">
-        <v>2.418</v>
+        <v>0</v>
       </c>
       <c r="D198">
-        <v>23998.7</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="1"/>
       <c r="B199" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>2.418</v>
       </c>
       <c r="D199">
-        <v>22352.79</v>
+        <v>23998.7</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="1"/>
       <c r="B200" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C200">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D200">
-        <v>15960</v>
+        <v>22352.79</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="1"/>
       <c r="B201" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C201">
-        <v>3.564</v>
+        <v>5</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>15960</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="1"/>
       <c r="B202" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>3.564</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -3071,142 +3071,142 @@
     <row r="203" spans="1:4">
       <c r="A203" s="1"/>
       <c r="B203" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C203">
-        <v>5.352</v>
+        <v>0</v>
       </c>
       <c r="D203">
-        <v>1562.512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="1"/>
       <c r="B204" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>5.352</v>
       </c>
       <c r="D204">
-        <v>10857</v>
+        <v>1562.512</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="1"/>
       <c r="B205" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C205">
         <v>0</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>10857</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="1"/>
       <c r="B206" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C206">
         <v>0</v>
       </c>
       <c r="D206">
-        <v>7359.999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="1"/>
       <c r="B207" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C207">
         <v>0</v>
       </c>
       <c r="D207">
-        <v>1200</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="1"/>
       <c r="B208" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C208">
         <v>0</v>
       </c>
       <c r="D208">
-        <v>2100</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="1"/>
       <c r="B209" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C209">
         <v>0</v>
       </c>
       <c r="D209">
-        <v>28320</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D210">
-        <v>10000</v>
+        <v>28320</v>
       </c>
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="1"/>
       <c r="B211" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D211">
-        <v>2700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="1"/>
       <c r="B212" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C212">
         <v>0</v>
       </c>
       <c r="D212">
-        <v>4800</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="1"/>
       <c r="B213" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C213">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="1"/>
       <c r="B214" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C214">
-        <v>0.064</v>
+        <v>2</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -3215,134 +3215,158 @@
     <row r="215" spans="1:4">
       <c r="A215" s="1"/>
       <c r="B215" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C215">
+        <v>0.064</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C215">
+      <c r="C216">
         <v>2.3</v>
       </c>
-      <c r="D215">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4">
-      <c r="A216" s="1" t="s">
+      <c r="D216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C216">
-        <v>0</v>
-      </c>
-      <c r="D216">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
-      <c r="A217" s="1"/>
       <c r="B217" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C217">
         <v>0</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>18538.462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="1"/>
       <c r="B218" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C218">
         <v>0</v>
       </c>
       <c r="D218">
-        <v>4296.908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="1"/>
       <c r="B219" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C219">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D219">
-        <v>12312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="1"/>
       <c r="B220" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C220">
         <v>0</v>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>4296.908</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="1"/>
       <c r="B221" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D221">
-        <v>7039.999999999999</v>
+        <v>12312</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="1"/>
       <c r="B222" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C222">
         <v>0</v>
       </c>
       <c r="D222">
-        <v>1200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="1"/>
       <c r="B223" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C223">
-        <v>-0.328</v>
+        <v>0</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>7039.999999999999</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C224">
         <v>0</v>
       </c>
       <c r="D224">
-        <v>20700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="1"/>
       <c r="B225" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C225">
+        <v>-0.328</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>20700</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C225">
+      <c r="C227">
         <v>-1</v>
       </c>
-      <c r="D225">
+      <c r="D227">
         <v>2391.799799999999</v>
       </c>
     </row>
@@ -3367,13 +3391,13 @@
     <mergeCell ref="A115:A125"/>
     <mergeCell ref="A126:A138"/>
     <mergeCell ref="A139:A149"/>
-    <mergeCell ref="A150:A159"/>
-    <mergeCell ref="A160:A166"/>
-    <mergeCell ref="A167:A180"/>
-    <mergeCell ref="A181:A188"/>
-    <mergeCell ref="A189:A195"/>
-    <mergeCell ref="A196:A215"/>
-    <mergeCell ref="A216:A225"/>
+    <mergeCell ref="A150:A160"/>
+    <mergeCell ref="A161:A167"/>
+    <mergeCell ref="A168:A181"/>
+    <mergeCell ref="A182:A189"/>
+    <mergeCell ref="A190:A196"/>
+    <mergeCell ref="A197:A216"/>
+    <mergeCell ref="A217:A227"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3403,7 +3427,7 @@
         <v>21.407</v>
       </c>
       <c r="C2">
-        <v>79340.10000000001</v>
+        <v>97878.56200000001</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4007,7 +4031,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>47940.7078</v>
+        <v>66479.1698</v>
       </c>
     </row>
     <row r="34" spans="1:2">
